--- a/data/trans_dic/POLIPATOLOGIA_Lim_5-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_5-Provincia-trans_dic.xlsx
@@ -524,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,91; 6,93</t>
+          <t>2,13; 6,91</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,88; 6,47</t>
+          <t>1,99; 6,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,26; 4,62</t>
+          <t>1,28; 4,59</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,3; 12,46</t>
+          <t>5,25; 12,62</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,64; 17,97</t>
+          <t>9,39; 17,58</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,09; 7,99</t>
+          <t>4,01; 7,83</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,35; 8,64</t>
+          <t>4,31; 8,46</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,47; 11,45</t>
+          <t>6,18; 11,16</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,91; 5,43</t>
+          <t>2,98; 5,46</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,1; 7,62</t>
+          <t>3,12; 7,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 2,1</t>
+          <t>0,34; 2,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,27; 7,4</t>
+          <t>3,19; 7,44</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 11,95</t>
+          <t>6,75; 11,92</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 8,07</t>
+          <t>3,7; 7,88</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,01; 15,67</t>
+          <t>11,01; 16,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,48; 8,91</t>
+          <t>5,59; 8,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,7</t>
+          <t>2,21; 4,63</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,59; 10,92</t>
+          <t>7,7; 10,9</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,24; 5,92</t>
+          <t>1,25; 5,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 3,45</t>
+          <t>0,53; 3,29</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 14,28</t>
+          <t>8,23; 14,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,37; 11,72</t>
+          <t>5,43; 11,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,0; 8,7</t>
+          <t>3,01; 8,62</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,22; 19,15</t>
+          <t>13,09; 19,17</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,94; 7,66</t>
+          <t>3,86; 7,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,14; 5,26</t>
+          <t>2,09; 5,14</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,8; 15,78</t>
+          <t>11,66; 16,06</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,27; 6,44</t>
+          <t>2,36; 6,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,83; 7,49</t>
+          <t>2,81; 7,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,58; 13,37</t>
+          <t>6,67; 13,05</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 17,74</t>
+          <t>10,39; 17,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,34; 16,35</t>
+          <t>9,5; 16,45</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 15,81</t>
+          <t>7,19; 15,88</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,81; 10,97</t>
+          <t>6,85; 11,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,66; 11,18</t>
+          <t>6,68; 11,09</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,55</t>
+          <t>8,04; 13,54</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>4,7; 12,68</t>
+          <t>5,06; 12,8</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 8,11</t>
+          <t>2,31; 8,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,85; 8,99</t>
+          <t>3,58; 8,73</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,77; 23,54</t>
+          <t>12,42; 23,56</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,46; 14,36</t>
+          <t>6,68; 15,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,73; 15,08</t>
+          <t>6,17; 15,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,54; 16,88</t>
+          <t>10,06; 17,19</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,09; 9,78</t>
+          <t>5,03; 10,26</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,12; 11,44</t>
+          <t>6,37; 11,56</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,64; 7,71</t>
+          <t>2,96; 8,37</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,0</t>
+          <t>1,15; 4,79</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>11,89; 18,41</t>
+          <t>12,1; 18,59</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,73; 9,8</t>
+          <t>3,75; 9,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,1; 10,3</t>
+          <t>4,07; 10,53</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,62; 29,4</t>
+          <t>21,54; 29,42</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,85; 7,83</t>
+          <t>3,88; 7,77</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>3,0; 6,74</t>
+          <t>2,91; 6,83</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,5; 22,51</t>
+          <t>17,46; 22,54</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,93</t>
+          <t>1,53; 3,94</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,59; 5,86</t>
+          <t>2,69; 6,05</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,19; 10,49</t>
+          <t>6,34; 10,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,87; 11,61</t>
+          <t>7,08; 11,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 11,3</t>
+          <t>6,99; 11,61</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>8,2; 21,75</t>
+          <t>7,68; 21,92</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,36</t>
+          <t>4,64; 7,32</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,35; 8,22</t>
+          <t>5,28; 8,17</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,15; 15,34</t>
+          <t>8,07; 15,47</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,94; 2,73</t>
+          <t>0,95; 2,79</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,06; 4,63</t>
+          <t>2,1; 4,6</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,35; 4,91</t>
+          <t>1,33; 4,92</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,55; 9,38</t>
+          <t>5,69; 9,34</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,97; 12,47</t>
+          <t>7,93; 12,51</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,6; 15,13</t>
+          <t>10,35; 14,68</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,57; 5,73</t>
+          <t>3,65; 5,72</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,49; 8,31</t>
+          <t>5,46; 8,16</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,51; 8,98</t>
+          <t>4,66; 9,13</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,91; 4,25</t>
+          <t>2,92; 4,31</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,53; 3,75</t>
+          <t>2,59; 3,76</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,16; 7,57</t>
+          <t>5,17; 7,62</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,24; 10,3</t>
+          <t>8,33; 10,28</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>7,94; 10,05</t>
+          <t>8,03; 10,11</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,25; 15,3</t>
+          <t>11,13; 15,28</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,86; 7,09</t>
+          <t>5,88; 7,06</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,49; 6,66</t>
+          <t>5,52; 6,69</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,1; 11,33</t>
+          <t>9,07; 11,41</t>
         </is>
       </c>
     </row>
@@ -1654,7 +1654,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante</t>
+          <t>Población con cinco o más enfermedades crónicas de las que al menos una es limitante (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>5633; 20437</t>
+          <t>6272; 20376</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5528; 19000</t>
+          <t>5849; 20386</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3926; 14389</t>
+          <t>3996; 14304</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15235; 35804</t>
+          <t>15073; 36262</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27826; 51868</t>
+          <t>27110; 50755</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11859; 23139</t>
+          <t>11604; 22668</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25325; 50280</t>
+          <t>25069; 49238</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>37702; 66711</t>
+          <t>36024; 65028</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17499; 32656</t>
+          <t>17910; 32814</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15647; 38510</t>
+          <t>15747; 37162</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1737; 10530</t>
+          <t>1729; 10687</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16947; 38345</t>
+          <t>16533; 38548</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>34566; 62574</t>
+          <t>35339; 62428</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19330; 42193</t>
+          <t>19340; 41214</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56703; 80713</t>
+          <t>56717; 82411</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>56446; 91739</t>
+          <t>57513; 91953</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22611; 48254</t>
+          <t>22650; 47508</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>78423; 112880</t>
+          <t>79573; 112638</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4015; 19186</t>
+          <t>4035; 17947</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2355; 10996</t>
+          <t>1677; 10477</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26005; 45118</t>
+          <t>26009; 45250</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18320; 39976</t>
+          <t>18527; 39834</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10087; 29250</t>
+          <t>10118; 28990</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>46148; 66874</t>
+          <t>45699; 66916</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>26171; 50973</t>
+          <t>25651; 49782</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>14034; 34467</t>
+          <t>13655; 33643</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>78470; 104933</t>
+          <t>77527; 106816</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8477; 24102</t>
+          <t>8839; 24773</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10486; 27728</t>
+          <t>10393; 27250</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20554; 41776</t>
+          <t>20860; 40790</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40883; 68985</t>
+          <t>40430; 66668</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36155; 63309</t>
+          <t>36798; 63693</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34138; 75201</t>
+          <t>34223; 75557</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>51967; 83702</t>
+          <t>52275; 85681</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50452; 84663</t>
+          <t>50615; 83952</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64553; 106804</t>
+          <t>63380; 106713</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10001; 26961</t>
+          <t>10754; 27216</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4734; 17122</t>
+          <t>4880; 17313</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6873; 16073</t>
+          <t>6392; 15611</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>28052; 51689</t>
+          <t>27268; 51741</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14113; 31381</t>
+          <t>14593; 33534</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>14818; 39015</t>
+          <t>15966; 39597</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>41247; 72952</t>
+          <t>43498; 74291</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21881; 42048</t>
+          <t>21638; 44096</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>26773; 50034</t>
+          <t>27883; 50579</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>7230; 21131</t>
+          <t>8109; 22933</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3156; 13168</t>
+          <t>3033; 12612</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32053; 49653</t>
+          <t>32633; 50128</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10454; 27454</t>
+          <t>10493; 27633</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11198; 28128</t>
+          <t>11121; 28757</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55588; 75572</t>
+          <t>55377; 75629</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21309; 43378</t>
+          <t>21472; 43025</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>16065; 36130</t>
+          <t>15625; 36614</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>92180; 118576</t>
+          <t>91954; 118691</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10123; 26050</t>
+          <t>10170; 26102</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17015; 38494</t>
+          <t>17654; 39735</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>38644; 65508</t>
+          <t>39585; 67517</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>47646; 80569</t>
+          <t>49144; 79637</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>48084; 78102</t>
+          <t>48292; 80229</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>69655; 184727</t>
+          <t>65203; 186144</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62976; 99868</t>
+          <t>62895; 99353</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>72105; 110744</t>
+          <t>71153; 110183</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>120042; 226072</t>
+          <t>118851; 227943</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7340; 21253</t>
+          <t>7437; 21723</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16004; 36039</t>
+          <t>16371; 35800</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12571; 45622</t>
+          <t>12314; 45704</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>45684; 77242</t>
+          <t>46901; 76948</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>65809; 103014</t>
+          <t>65556; 103380</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>76102; 108592</t>
+          <t>74287; 105351</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57255; 91876</t>
+          <t>58532; 91617</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>88054; 133325</t>
+          <t>87616; 130983</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>74192; 147844</t>
+          <t>76658; 150280</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>99877; 145479</t>
+          <t>99908; 147553</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>85975; 127247</t>
+          <t>87899; 127715</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>178594; 261829</t>
+          <t>178838; 263678</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>293090; 366377</t>
+          <t>296365; 365898</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>281573; 356245</t>
+          <t>284649; 358179</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>417804; 567954</t>
+          <t>413012; 567137</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>409542; 495356</t>
+          <t>410937; 492949</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>380773; 462015</t>
+          <t>382863; 464351</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>652587; 812477</t>
+          <t>650438; 818617</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/POLIPATOLOGIA_Lim_5-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/POLIPATOLOGIA_Lim_5-Provincia-trans_dic.xlsx
@@ -635,7 +635,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -650,7 +650,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -678,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,13; 6,91</t>
+          <t>1,96; 6,87</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,94</t>
+          <t>2,04; 6,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,28; 4,59</t>
+          <t>1,21; 4,55</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 12,62</t>
+          <t>5,21; 12,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,39; 17,58</t>
+          <t>9,16; 17,88</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,01; 7,83</t>
+          <t>4,2; 7,8</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,31; 8,46</t>
+          <t>4,27; 8,38</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 11,16</t>
+          <t>6,23; 11,07</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,98; 5,46</t>
+          <t>3,03; 5,52</t>
         </is>
       </c>
     </row>
@@ -745,7 +745,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>12,92%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -775,7 +775,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>3,12; 7,35</t>
+          <t>3,1; 7,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,13</t>
+          <t>0,34; 2,16</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>3,19; 7,44</t>
+          <t>3,52; 7,81</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>6,75; 11,92</t>
+          <t>6,57; 11,82</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,7; 7,88</t>
+          <t>3,45; 7,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,01; 16,0</t>
+          <t>10,68; 15,57</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,59; 8,93</t>
+          <t>5,59; 8,96</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,63</t>
+          <t>2,17; 4,44</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>7,7; 10,9</t>
+          <t>7,52; 10,87</t>
         </is>
       </c>
     </row>
@@ -855,7 +855,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -885,7 +885,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>13,59%</t>
+          <t>13,49%</t>
         </is>
       </c>
     </row>
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,54</t>
+          <t>1,24; 5,25</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,29</t>
+          <t>0,54; 3,17</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>8,23; 14,32</t>
+          <t>8,21; 14,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,43; 11,68</t>
+          <t>5,3; 11,56</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 8,62</t>
+          <t>3,15; 9,07</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,09; 19,17</t>
+          <t>13,07; 19,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3,86; 7,49</t>
+          <t>3,94; 7,71</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 5,14</t>
+          <t>2,2; 5,23</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>11,66; 16,06</t>
+          <t>11,53; 15,59</t>
         </is>
       </c>
     </row>
@@ -965,7 +965,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -980,7 +980,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>12,21%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -995,7 +995,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,88%</t>
         </is>
       </c>
     </row>
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,36; 6,62</t>
+          <t>2,38; 6,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,81; 7,37</t>
+          <t>2,93; 7,28</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6,67; 13,05</t>
+          <t>6,21; 12,15</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>10,39; 17,14</t>
+          <t>10,16; 17,09</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>9,5; 16,45</t>
+          <t>9,24; 16,6</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,19; 15,88</t>
+          <t>12,47; 17,67</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>6,85; 11,23</t>
+          <t>6,98; 11,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>6,68; 11,09</t>
+          <t>7,0; 11,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>8,04; 13,54</t>
+          <t>10,04; 13,83</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>11,46%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1105,7 +1105,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>9,16%</t>
+          <t>9,45%</t>
         </is>
       </c>
     </row>
@@ -1118,47 +1118,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,06; 12,8</t>
+          <t>4,81; 12,56</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,31; 8,2</t>
+          <t>2,3; 8,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>3,58; 8,73</t>
+          <t>3,22; 7,91</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>12,42; 23,56</t>
+          <t>13,1; 23,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>6,68; 15,34</t>
+          <t>6,54; 15,01</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,17; 15,3</t>
+          <t>10,42; 15,88</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,06; 17,19</t>
+          <t>10,0; 16,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 10,26</t>
+          <t>5,05; 9,91</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>6,37; 11,56</t>
+          <t>7,74; 11,51</t>
         </is>
       </c>
     </row>
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1215,7 +1215,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -1228,47 +1228,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>2,96; 8,37</t>
+          <t>2,64; 7,95</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,15; 4,79</t>
+          <t>1,2; 5,3</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>12,1; 18,59</t>
+          <t>11,8; 18,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>3,75; 9,87</t>
+          <t>4,04; 9,68</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>4,07; 10,53</t>
+          <t>3,78; 10,26</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>21,54; 29,42</t>
+          <t>21,51; 29,49</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,88; 7,77</t>
+          <t>3,76; 8,06</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,91; 6,83</t>
+          <t>3,11; 6,71</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>17,46; 22,54</t>
+          <t>17,76; 22,77</t>
         </is>
       </c>
     </row>
@@ -1295,7 +1295,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1325,7 +1325,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>14,69%</t>
         </is>
       </c>
     </row>
@@ -1338,47 +1338,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,94</t>
+          <t>1,54; 4,29</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,69; 6,05</t>
+          <t>2,65; 5,75</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6,34; 10,82</t>
+          <t>6,26; 10,31</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,08; 11,48</t>
+          <t>6,96; 11,3</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,99; 11,61</t>
+          <t>7,15; 11,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,68; 21,92</t>
+          <t>18,31; 23,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>4,64; 7,32</t>
+          <t>4,66; 7,51</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>5,28; 8,17</t>
+          <t>5,43; 8,21</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>8,07; 15,47</t>
+          <t>13,01; 16,37</t>
         </is>
       </c>
     </row>
@@ -1405,7 +1405,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>8,01%</t>
         </is>
       </c>
     </row>
@@ -1448,47 +1448,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,95; 2,79</t>
+          <t>0,84; 2,88</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,6</t>
+          <t>2,04; 4,78</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1,33; 4,92</t>
+          <t>3,22; 5,79</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5,69; 9,34</t>
+          <t>5,41; 9,29</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,93; 12,51</t>
+          <t>7,99; 12,37</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,35; 14,68</t>
+          <t>9,79; 13,39</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,65; 5,72</t>
+          <t>3,59; 5,66</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,46; 8,16</t>
+          <t>5,47; 8,07</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>4,66; 9,13</t>
+          <t>6,91; 9,12</t>
         </is>
       </c>
     </row>
@@ -1515,7 +1515,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>6,98%</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,12%</t>
         </is>
       </c>
     </row>
@@ -1558,47 +1558,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>2,92; 4,31</t>
+          <t>2,95; 4,36</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,59; 3,76</t>
+          <t>2,51; 3,81</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>5,17; 7,62</t>
+          <t>6,2; 7,73</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8,33; 10,28</t>
+          <t>8,36; 10,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>8,03; 10,11</t>
+          <t>7,95; 10,02</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>11,13; 15,28</t>
+          <t>14,09; 15,98</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,88; 7,06</t>
+          <t>5,9; 7,12</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5,52; 6,69</t>
+          <t>5,52; 6,72</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>9,07; 11,41</t>
+          <t>10,49; 11,77</t>
         </is>
       </c>
     </row>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7592</t>
+          <t>7931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16774</t>
+          <t>18484</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24366</t>
+          <t>26415</t>
         </is>
       </c>
     </row>
@@ -1861,47 +1861,47 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>6272; 20376</t>
+          <t>5776; 20255</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>5849; 20386</t>
+          <t>5993; 19644</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3996; 14304</t>
+          <t>3873; 14505</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15073; 36262</t>
+          <t>14978; 36198</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>27110; 50755</t>
+          <t>26453; 51624</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>11604; 22668</t>
+          <t>13284; 24659</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25069; 49238</t>
+          <t>24844; 48777</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36024; 65028</t>
+          <t>36261; 64497</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>17910; 32814</t>
+          <t>19245; 35043</t>
         </is>
       </c>
     </row>
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>26343</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67767</t>
+          <t>70617</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>94110</t>
+          <t>98791</t>
         </is>
       </c>
     </row>
@@ -2024,47 +2024,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>15747; 37162</t>
+          <t>15647; 38322</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1729; 10687</t>
+          <t>1732; 10834</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16533; 38548</t>
+          <t>18673; 41432</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>35339; 62428</t>
+          <t>34431; 61905</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19340; 41214</t>
+          <t>18032; 40542</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>56717; 82411</t>
+          <t>58391; 85114</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>57513; 91953</t>
+          <t>57496; 92236</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>22650; 47508</t>
+          <t>22246; 45549</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>79573; 112638</t>
+          <t>80979; 117112</t>
         </is>
       </c>
     </row>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>34542</t>
+          <t>34187</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2159,7 +2159,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55881</t>
+          <t>56545</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>90422</t>
+          <t>90733</t>
         </is>
       </c>
     </row>
@@ -2187,47 +2187,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4035; 17947</t>
+          <t>4032; 17027</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1677; 10477</t>
+          <t>1730; 10110</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>26009; 45250</t>
+          <t>25958; 44578</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>18527; 39834</t>
+          <t>18061; 39421</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>10118; 28990</t>
+          <t>10596; 30508</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>45699; 66916</t>
+          <t>46596; 68516</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25651; 49782</t>
+          <t>26184; 51252</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>13655; 33643</t>
+          <t>14414; 34276</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>77527; 106816</t>
+          <t>77554; 104839</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>29905</t>
+          <t>32397</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>58078</t>
+          <t>62063</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -2337,7 +2337,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>87983</t>
+          <t>94460</t>
         </is>
       </c>
     </row>
@@ -2350,47 +2350,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>8839; 24773</t>
+          <t>8918; 24555</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>10393; 27250</t>
+          <t>10849; 26928</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>20860; 40790</t>
+          <t>23162; 45336</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>40430; 66668</t>
+          <t>39517; 66477</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>36798; 63693</t>
+          <t>35771; 64292</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>34223; 75557</t>
+          <t>52624; 74565</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>52275; 85681</t>
+          <t>53220; 84023</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>50615; 83952</t>
+          <t>52978; 84243</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>63380; 106713</t>
+          <t>79821; 109994</t>
         </is>
       </c>
     </row>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>10416</t>
+          <t>10895</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>29659</t>
+          <t>30172</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>40075</t>
+          <t>41067</t>
         </is>
       </c>
     </row>
@@ -2513,47 +2513,47 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>10754; 27216</t>
+          <t>10217; 26699</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>4880; 17313</t>
+          <t>4854; 16910</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6392; 15611</t>
+          <t>6631; 16276</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>27268; 51741</t>
+          <t>28777; 51393</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>14593; 33534</t>
+          <t>14301; 32808</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>15966; 39597</t>
+          <t>23856; 36361</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>43498; 74291</t>
+          <t>43209; 70298</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>21638; 44096</t>
+          <t>21696; 42587</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>27883; 50579</t>
+          <t>33658; 50017</t>
         </is>
       </c>
     </row>
@@ -2633,7 +2633,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40322</t>
+          <t>40466</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>64768</t>
+          <t>66783</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2663,7 +2663,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>105090</t>
+          <t>107249</t>
         </is>
       </c>
     </row>
@@ -2676,47 +2676,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>8109; 22933</t>
+          <t>7223; 21768</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>3033; 12612</t>
+          <t>3169; 13943</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>32633; 50128</t>
+          <t>31937; 50106</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10493; 27633</t>
+          <t>11324; 27113</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>11121; 28757</t>
+          <t>10319; 28011</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>55377; 75629</t>
+          <t>56732; 77788</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21472; 43025</t>
+          <t>20839; 44675</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>15625; 36614</t>
+          <t>16675; 35956</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>91954; 118691</t>
+          <t>94924; 121714</t>
         </is>
       </c>
     </row>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>51347</t>
+          <t>58429</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>135634</t>
+          <t>160689</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2826,7 +2826,7 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>186981</t>
+          <t>219118</t>
         </is>
       </c>
     </row>
@@ -2839,47 +2839,47 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>10170; 26102</t>
+          <t>10221; 28415</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>17654; 39735</t>
+          <t>17387; 37735</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>39585; 67517</t>
+          <t>45077; 74229</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49144; 79637</t>
+          <t>48260; 78438</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>48292; 80229</t>
+          <t>49460; 80050</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65203; 186144</t>
+          <t>141370; 182768</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>62895; 99353</t>
+          <t>63237; 101825</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>71153; 110183</t>
+          <t>73202; 110631</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>118851; 227943</t>
+          <t>194092; 244147</t>
         </is>
       </c>
     </row>
@@ -2959,7 +2959,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>30063</t>
+          <t>34222</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -2974,7 +2974,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>89033</t>
+          <t>96313</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>119097</t>
+          <t>130535</t>
         </is>
       </c>
     </row>
@@ -3002,47 +3002,47 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>7437; 21723</t>
+          <t>6510; 22433</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>16371; 35800</t>
+          <t>15916; 37219</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>12314; 45704</t>
+          <t>25701; 46174</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>46901; 76948</t>
+          <t>44591; 76561</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>65556; 103380</t>
+          <t>65984; 102162</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>74287; 105351</t>
+          <t>81403; 111329</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>58532; 91617</t>
+          <t>57564; 90759</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>87616; 130983</t>
+          <t>87716; 129432</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>76658; 150280</t>
+          <t>112593; 148640</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>230531</t>
+          <t>246701</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>517594</t>
+          <t>561666</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>748125</t>
+          <t>808367</t>
         </is>
       </c>
     </row>
@@ -3165,47 +3165,47 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>99908; 147553</t>
+          <t>101165; 149257</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>87899; 127715</t>
+          <t>85097; 129311</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>178838; 263678</t>
+          <t>219051; 273162</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>296365; 365898</t>
+          <t>297365; 371449</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>284649; 358179</t>
+          <t>281670; 355091</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>413012; 567137</t>
+          <t>526629; 597294</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>410937; 492949</t>
+          <t>412347; 497420</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
         <is>
-          <t>382863; 464351</t>
+          <t>383156; 466397</t>
         </is>
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>650438; 818617</t>
+          <t>762491; 855960</t>
         </is>
       </c>
     </row>
